--- a/Data/Building/MeetingRoomOne.Curtain001.xlsx
+++ b/Data/Building/MeetingRoomOne.Curtain001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H126"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709258835</v>
+        <v>1711850433</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709261034</v>
+        <v>1711850529</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709262223</v>
+        <v>1711851968</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -574,9 +581,10 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709267188</v>
+        <v>1711859831</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709268147</v>
+        <v>1711860778</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709249519</v>
+        <v>1711927999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709251714</v>
+        <v>1711930316</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +732,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709253107</v>
+        <v>1711931411</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709258666</v>
+        <v>1711932287</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -790,9 +803,10 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709259199</v>
+        <v>1711933169</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +843,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709259274</v>
+        <v>1711934819</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +880,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709260507</v>
+        <v>1711936103</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +917,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709261128</v>
+        <v>1711938757</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +954,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +973,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709336433</v>
+        <v>1712014747</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +991,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1010,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709339112</v>
+        <v>1712016964</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1028,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1047,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709339139</v>
+        <v>1712018823</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1065,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1084,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709340135</v>
+        <v>1712023346</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1078,9 +1099,10 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1121,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709344291</v>
+        <v>1712024575</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1117,6 +1139,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1158,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709346037</v>
+        <v>1712025631</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1150,9 +1173,10 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1195,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709347174</v>
+        <v>1712102412</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1189,6 +1213,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1232,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709348838</v>
+        <v>1712104062</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1225,6 +1250,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1269,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709425447</v>
+        <v>1712106536</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1287,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1306,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709426177</v>
+        <v>1712109015</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1294,9 +1321,10 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1343,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709430712</v>
+        <v>1712110987</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1333,6 +1361,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1380,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709432788</v>
+        <v>1712112245</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1366,9 +1395,10 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1417,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709434121</v>
+        <v>1712186115</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1405,6 +1435,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1423,7 +1454,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709435826</v>
+        <v>1712188711</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1441,6 +1472,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1491,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709508376</v>
+        <v>1712191421</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1477,6 +1509,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1528,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709509888</v>
+        <v>1712193903</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1513,6 +1546,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1565,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709511649</v>
+        <v>1712195632</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1549,6 +1583,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1602,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709511930</v>
+        <v>1712197528</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1582,9 +1617,10 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1639,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709518723</v>
+        <v>1712272844</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1621,6 +1657,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1676,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709520130</v>
+        <v>1712274067</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1657,6 +1694,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1675,7 +1713,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709520447</v>
+        <v>1712282560</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1693,6 +1731,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1711,7 +1750,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709521583</v>
+        <v>1712282818</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1726,9 +1765,10 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1747,7 +1787,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709596582</v>
+        <v>1712284171</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1765,6 +1805,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1824,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709601695</v>
+        <v>1712285323</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1798,9 +1839,10 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1861,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709607992</v>
+        <v>1712533699</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1879,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1898,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709608592</v>
+        <v>1712536884</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1870,9 +1913,10 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +1935,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709852795</v>
+        <v>1712537001</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1909,6 +1953,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +1972,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709855104</v>
+        <v>1712537922</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1945,6 +1990,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2009,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709855665</v>
+        <v>1712539453</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1981,6 +2027,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1999,7 +2046,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709856509</v>
+        <v>1712539575</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2017,6 +2064,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2035,7 +2083,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709860882</v>
+        <v>1712621516</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2053,6 +2101,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2071,7 +2120,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709862229</v>
+        <v>1712623461</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2089,6 +2138,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2107,7 +2157,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709862578</v>
+        <v>1712625120</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2125,6 +2175,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2143,7 +2194,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709865542</v>
+        <v>1712627729</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2158,9 +2209,10 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2179,7 +2231,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709942706</v>
+        <v>1712628040</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2197,6 +2249,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2215,7 +2268,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709944954</v>
+        <v>1712628044</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2233,6 +2286,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2251,7 +2305,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709950410</v>
+        <v>1712630440</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2269,6 +2323,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2287,7 +2342,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709951583</v>
+        <v>1712632657</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2302,9 +2357,10 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2323,7 +2379,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710028021</v>
+        <v>1712707864</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2341,6 +2397,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2359,7 +2416,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710031633</v>
+        <v>1712709395</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2377,6 +2434,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2395,7 +2453,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710040546</v>
+        <v>1712716899</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2413,6 +2471,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2431,7 +2490,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710040571</v>
+        <v>1712720304</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2446,9 +2505,10 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2467,7 +2527,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710116180</v>
+        <v>1712795978</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2485,6 +2545,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2503,7 +2564,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710116319</v>
+        <v>1712798474</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2521,6 +2582,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2539,7 +2601,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710125689</v>
+        <v>1712804017</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2557,6 +2619,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2575,7 +2638,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710130126</v>
+        <v>1712806020</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2593,6 +2656,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2611,7 +2675,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710200225</v>
+        <v>1712806031</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2629,6 +2693,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2647,7 +2712,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710203243</v>
+        <v>1712806520</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2665,6 +2730,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2683,7 +2749,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710204418</v>
+        <v>1712879337</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2701,6 +2767,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2719,7 +2786,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710204735</v>
+        <v>1712881901</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2734,9 +2801,10 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2755,7 +2823,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710207419</v>
+        <v>1712883549</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2773,6 +2841,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2791,7 +2860,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710209722</v>
+        <v>1712885386</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2809,6 +2878,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2827,7 +2897,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710211238</v>
+        <v>1712887165</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2845,6 +2915,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2863,7 +2934,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710212713</v>
+        <v>1712888483</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2881,6 +2952,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2899,7 +2971,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710459995</v>
+        <v>1713139106</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2917,6 +2989,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2935,7 +3008,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710461367</v>
+        <v>1713141365</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2950,9 +3023,10 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2971,7 +3045,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710469226</v>
+        <v>1713147419</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2989,6 +3063,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3007,7 +3082,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710470207</v>
+        <v>1713148283</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3025,6 +3100,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3043,7 +3119,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710470303</v>
+        <v>1713148480</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3061,6 +3137,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3079,7 +3156,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710470637</v>
+        <v>1713150862</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3094,9 +3171,10 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3115,7 +3193,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710548576</v>
+        <v>1713223478</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3133,6 +3211,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3151,7 +3230,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710549709</v>
+        <v>1713227623</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3169,6 +3248,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3187,7 +3267,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710553376</v>
+        <v>1713230282</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3205,6 +3285,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3223,7 +3304,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710557335</v>
+        <v>1713234399</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3241,6 +3322,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3259,7 +3341,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710634166</v>
+        <v>1713310748</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3277,6 +3359,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3295,7 +3378,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710636930</v>
+        <v>1713313598</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3313,6 +3396,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3331,7 +3415,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710638910</v>
+        <v>1713313837</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3349,6 +3433,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3367,7 +3452,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710641256</v>
+        <v>1713314040</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3382,9 +3467,10 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3403,7 +3489,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710642711</v>
+        <v>1713319591</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3421,6 +3507,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3439,7 +3526,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710644228</v>
+        <v>1713320974</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3454,9 +3541,10 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3475,7 +3563,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710644998</v>
+        <v>1713395544</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3493,6 +3581,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3511,7 +3600,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710645006</v>
+        <v>1713397250</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3529,6 +3618,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3547,7 +3637,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710719548</v>
+        <v>1713397673</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3565,6 +3655,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3583,7 +3674,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710721590</v>
+        <v>1713399596</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3601,6 +3692,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3619,7 +3711,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710728847</v>
+        <v>1713403933</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3637,6 +3729,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3655,7 +3748,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710730443</v>
+        <v>1713405994</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3673,6 +3766,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3691,7 +3785,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710805950</v>
+        <v>1713484675</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3709,6 +3803,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3727,7 +3822,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710807920</v>
+        <v>1713486046</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3745,6 +3840,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3763,7 +3859,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710815405</v>
+        <v>1713486134</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3781,6 +3877,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3799,7 +3896,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710815484</v>
+        <v>1713488129</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3814,9 +3911,10 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3835,7 +3933,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710815686</v>
+        <v>1713488157</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3853,6 +3951,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3871,7 +3970,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710817587</v>
+        <v>1713488194</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3886,9 +3985,10 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3907,7 +4007,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1711064088</v>
+        <v>1713492022</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3925,6 +4025,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3943,7 +4044,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1711065643</v>
+        <v>1713494228</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3961,6 +4062,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3979,7 +4081,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1711067201</v>
+        <v>1713741786</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3997,6 +4099,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4015,7 +4118,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1711068271</v>
+        <v>1713743195</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4033,6 +4136,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4051,7 +4155,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1711072652</v>
+        <v>1713744173</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4069,6 +4173,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4087,7 +4192,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1711073049</v>
+        <v>1713744365</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4105,6 +4210,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4123,7 +4229,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1711073736</v>
+        <v>1713745596</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4141,6 +4247,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4159,7 +4266,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1711074661</v>
+        <v>1713745819</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4174,9 +4281,10 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4195,7 +4303,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1711150334</v>
+        <v>1713750207</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4213,6 +4321,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4231,7 +4340,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1711152607</v>
+        <v>1713752399</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4249,6 +4358,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4267,7 +4377,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1711153443</v>
+        <v>1713831809</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4285,6 +4395,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4303,7 +4414,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1711163338</v>
+        <v>1713832444</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4321,6 +4432,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4339,7 +4451,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1711236336</v>
+        <v>1713833172</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4357,6 +4469,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4375,7 +4488,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1711238249</v>
+        <v>1713835274</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4393,6 +4506,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4411,7 +4525,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1711241185</v>
+        <v>1713837291</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4429,6 +4543,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4447,7 +4562,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1711241246</v>
+        <v>1713839856</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4462,9 +4577,10 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4483,7 +4599,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1711243024</v>
+        <v>1713840451</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4501,6 +4617,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4519,7 +4636,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1711248835</v>
+        <v>1713842750</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4537,6 +4654,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4555,7 +4673,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1711323225</v>
+        <v>1713915096</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4573,6 +4691,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4591,7 +4710,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1711324816</v>
+        <v>1713917154</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4609,6 +4728,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4627,7 +4747,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1711326601</v>
+        <v>1713925908</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4645,6 +4765,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4663,7 +4784,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1711328562</v>
+        <v>1713925924</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4681,6 +4802,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4699,7 +4821,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1711334705</v>
+        <v>1713926583</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4717,6 +4839,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4735,7 +4858,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1711335303</v>
+        <v>1713927657</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4753,6 +4876,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4771,7 +4895,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1711410245</v>
+        <v>1714000527</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4789,6 +4913,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4807,7 +4932,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1711415164</v>
+        <v>1714002128</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4822,9 +4947,10 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4843,7 +4969,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1711416873</v>
+        <v>1714002186</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4861,6 +4987,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4879,7 +5006,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1711418509</v>
+        <v>1714002410</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4894,9 +5021,10 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4915,7 +5043,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1711420494</v>
+        <v>1714003384</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4933,6 +5061,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4951,7 +5080,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1711421672</v>
+        <v>1714004128</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4969,6 +5098,303 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>MeetingRoomOne</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1714004253</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>MeetingRoomOne.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>MeetingRoomOne</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1714006866</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>MeetingRoomOne.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>MeetingRoomOne</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1714007324</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>MeetingRoomOne.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>MeetingRoomOne</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1714010026</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>MeetingRoomOne.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>MeetingRoomOne</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1714089541</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>MeetingRoomOne.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>MeetingRoomOne</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1714090639</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>MeetingRoomOne.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>MeetingRoomOne</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1714095792</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>MeetingRoomOne.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>MeetingRoomOne</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1714097714</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>MeetingRoomOne.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
